--- a/artfynd/A 25285-2023 artfynd.xlsx
+++ b/artfynd/A 25285-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25285-2023 artfynd.xlsx
+++ b/artfynd/A 25285-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>111936769</v>
       </c>
       <c r="B2" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111936773</v>
+        <v>111936770</v>
       </c>
       <c r="B3" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490003</v>
+        <v>489836</v>
       </c>
       <c r="R3" t="n">
-        <v>7087487</v>
+        <v>7087463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +860,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack gamla</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,12 +890,7 @@
         <v>111936772</v>
       </c>
       <c r="B4" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111936770</v>
+        <v>111936773</v>
       </c>
       <c r="B5" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489837</v>
+        <v>490003</v>
       </c>
       <c r="R5" t="n">
-        <v>7087463</v>
+        <v>7087487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1072,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack gamla</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 25285-2023 artfynd.xlsx
+++ b/artfynd/A 25285-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936769</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936770</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936772</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936773</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>